--- a/Kostenaufstellung_Hardware.xlsx
+++ b/Kostenaufstellung_Hardware.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SourceCode\IoT_Projekt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samsf/DEV/IOT/IoT_Projekt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395A8635-5AAD-478B-B60C-ECC595507D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD34794-3371-274D-88B7-40D5648D7B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>Artikelname</t>
   </si>
@@ -71,13 +71,19 @@
     <t>Div. Kleinteile</t>
   </si>
   <si>
-    <t>Nerfen</t>
-  </si>
-  <si>
     <t>Kostenaufstellung IOT Gehirnzellenmassaker Haris</t>
   </si>
   <si>
     <t>Kostenaufstellung IOT Gehirnzellenmassaker Elias</t>
+  </si>
+  <si>
+    <t>Winkel</t>
+  </si>
+  <si>
+    <t>Holz</t>
+  </si>
+  <si>
+    <t>Kostenaufstellung IOT Gehirnzellenmassaker Felix</t>
   </si>
 </sst>
 </file>
@@ -87,11 +93,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* &quot;-&quot;??\ [$€-407]_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -247,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -270,9 +283,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -485,32 +502,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:L23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18" bestFit="1"/>
     <col min="5" max="5" width="15" bestFit="1"/>
-    <col min="7" max="7" width="9.109375" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="19.44140625" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="12" max="12" width="17.5" customWidth="1"/>
+    <col min="15" max="16" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
       <c r="E2" s="15"/>
       <c r="I2" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
       <c r="L2" s="15"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,7 +548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
@@ -550,7 +568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
@@ -558,7 +576,7 @@
         <v>14.77</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="5">
@@ -566,7 +584,7 @@
       </c>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -578,7 +596,7 @@
       <c r="J6" s="5"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
@@ -586,31 +604,29 @@
         <v>42.18</v>
       </c>
       <c r="E7" s="7"/>
-      <c r="I7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="9"/>
+      <c r="C8" s="9">
+        <v>0.5</v>
+      </c>
       <c r="E8" s="7"/>
       <c r="I8" s="8"/>
       <c r="J8" s="9"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5">
         <f>SUM(C4:C8)</f>
-        <v>76.990000000000009</v>
+        <v>77.490000000000009</v>
       </c>
       <c r="E9" s="7"/>
       <c r="I9" s="4" t="s">
@@ -622,13 +638,13 @@
       </c>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="10">
         <f>$C$9/$E$4</f>
-        <v>19.247500000000002</v>
+        <v>19.372500000000002</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="2"/>
@@ -642,34 +658,102 @@
       <c r="K10" s="11"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C11" s="12"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C12" s="12"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C13" s="12"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C14" s="12"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C15" s="12"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="12"/>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" s="12"/>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" s="12"/>
+    <row r="15" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5">
+        <v>15</v>
+      </c>
+      <c r="E17" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="5">
+        <v>5</v>
+      </c>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2</v>
+      </c>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <f>SUM(C17:C21)</f>
+        <v>22</v>
+      </c>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="10">
+        <f>$J$9/$L$4</f>
+        <v>6.2374999999999998</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="I2:L2"/>
+    <mergeCell ref="B15:E15"/>
   </mergeCells>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
